--- a/c1000-183-image-prompts.xlsx
+++ b/c1000-183-image-prompts.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -604,6 +604,83 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="220" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-3-2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-3-2.svg</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Options Site-level dans Organizations app</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Isometric infographic showing the IBM Maximo Manage Organizations application as a central control panel with two distinct branches emerging from a Select Action menu. Top branch labeled 'Org-level' (amber color theme) shows 4 stylized icons: Chart of Accounts (column chart), Taxes (percent symbol), Workflow Settings (flow diagram), GL Configuration (ledger book). Bottom branch labeled 'Site-level' (teal color theme) shows 4 stylized icons: Work Order Options (clipboard), Inventory Options (boxes), Purchasing Options (cart), Bulletin Board (notice board). Two small site cubes at the bottom right (NYC and LA) showing how site-level options can differ between sites of the same Organization.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching the lesson 3.1 visual language. Vector flat with soft depth shading. Stripe Press / Linear marketing infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Center: Organizations app icon (server/console metaphor) with Select Action dropdown opened. Top branching flow: 4 amber-tinted Org-level option icons in a horizontal row. Bottom branching flow: 4 teal-tinted Site-level option icons in a horizontal row. Bottom-right corner: 2 small site cubes (NYC, LA) with subtle differentiation showing Site-level customization. Generous 80px padding. Subtle topographic line pattern background at 5% opacity.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75 (Site-level branch + sites), accent amber #F59E0B (Org-level branch + central console), neutral slate #475569 for connecting lines and labels, white #FFFFFF background, brand topographic teal #1D9E75 at 5% alpha for background.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion under each option icon</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. No raster textures. Visual coherence with lesson 3.1 hero (same color palette, same isometric style, same line weight).</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>no people, no faces, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks, no 3D render look, no skeuomorphism, no neon glows, no chromatic aberration</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Organizations Application https://www.ibm.com/docs/en/maximo-manage/9.0.0?topic=organizations-overview ; lesson 3.1 hero (visual coherence) ; Stripe Press infographics ; Linear.app marketing</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Hero image for lesson 3.2. The dual branch (Org-level vs Site-level) must be visually distinct via color coding (amber vs teal). Site cubes at bottom-right reinforce that Site-level options can vary between sites. Match the visual language of lesson 3.1 hero for series coherence.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/c1000-183-image-prompts.xlsx
+++ b/c1000-183-image-prompts.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -681,6 +681,83 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="220" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-3-3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-3-3.svg</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Chaîne de sécurité Person → User → Group → Start Center</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Isometric flow diagram showing the IBM Maximo Manage 4-link security chain: a stylized human silhouette icon (Person) with an ID badge, connecting via arrow to a key/lock icon (User login), connecting to a group of figures icon (Security Group with permission shields), connecting to a dashboard/screen icon (Start Center showing widgets). 4 entities arranged horizontally in a clear left-to-right flow with arrows. Each entity has a small label tag below showing the app name (People / Users / Security Groups / Start Centers). Subtle indicators showing FK constraints between entities (small chain link motifs).</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching lessons 3.1 and 3.2 visual language. Vector flat with soft depth shading. Stripe Press / Linear marketing infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Horizontal flow left to right, 4 entities at equal spacing. Person icon on left (blue tint), User icon (gray tint), Security Group icon (amber tint), Start Center icon (teal tint). Arrows between entities with small FK chain motifs. App name labels below each entity. Light subtle background with topographic teal pattern at 5% opacity.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Person blue #3B82F6, User slate gray #475569, Security Group amber #F59E0B, Start Center teal #1D9E75, white background, brand topographic teal at 5% alpha. Color progression matches the 4-level storage hierarchy from lesson 3.1.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion under each icon</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1 and 3.2 hero illustrations (same color system, same isometric perspective).</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features (use silhouette), no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no trademarks, no 3D render look, no skeuomorphism, no neon glows</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Security Groups https://www.ibm.com/docs/en/maximo-manage/9.0.0?topic=security-security-groups ; lessons 3.1 and 3.2 hero (visual coherence) ; Stripe Press infographics</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Hero image for lesson 3.3. The 4-link chain Person → User → Group → Start Center must be unambiguous via the directional flow. Color progression respects the lesson 3.1 hierarchy (blue=System equivalent, gray=intermediate, amber=group, teal=interface). Keep the human silhouette generic — no faces, no ethnicity markers.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/c1000-183-image-prompts.xlsx
+++ b/c1000-183-image-prompts.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -758,6 +758,83 @@
         </is>
       </c>
     </row>
+    <row r="5" ht="220" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-3-4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-3-4.svg</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Calendars centraux + 5 modules consumers</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Isometric hub-and-spoke diagram showing the IBM Maximo Manage Calendars application as a central hub (clock/calendar icon with working hours grid visible) with 5 spokes radiating outward to consumer modules: Labor (worker silhouette), Preventive Maintenance (wrench + calendar), SLA (stopwatch), Escalation (warning bell), Scheduler (Gantt chart). Each spoke is a labeled arrow showing the FK reference (CALNUM or SHIFTNUM). Background subtly hints at the working time pattern (small grid of cells, some highlighted as working, some grayed as non-working including a holiday marker).</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching the C1000-183 series visual language. Vector flat with soft depth shading. Stripe Press / Linear marketing infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Center: large Calendars hub icon (amber tint) with visible 7-day grid showing some cells as working (teal) and some as non-working (gray). 5 arrows radiating to 5 consumer module icons positioned at clock-position 11-12-1-2-4 around the hub. Small FK labels on each arrow (CALNUM, SHIFTNUM). Subtle topographic line pattern background at 5% opacity.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Calendars hub amber #F59E0B (Org-level color from lesson 3.2), consumer modules teal #1D9E75 (Site-level color), arrows slate gray #475569, working cells teal #1D9E75, non-working cells light gray #CBD5E1, holiday marker red #EF4444 hint, white background, topographic pattern at 5% alpha.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion under hub and modules</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1, 3.2, 3.3 hero (same color system, same isometric perspective).</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks, no 3D render look, no skeuomorphism, no neon glows</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Calendars https://www.ibm.com/docs/en/maximo-manage/9.0.0?topic=calendars-creating ; lessons 3.1-3.3 hero (visual coherence) ; Stripe Press infographics</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Hero image for lesson 3.4. The hub-and-spoke pattern is critical — viewers must immediately grasp that Calendars is the central source of truth and 5 modules consume it. Color the hub in amber (Org-level / structural) and the consumers in teal (operational / Site-level) for visual coherence with lesson 3.2.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/c1000-183-image-prompts.xlsx
+++ b/c1000-183-image-prompts.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -835,6 +835,83 @@
         </is>
       </c>
     </row>
+    <row r="6" ht="220" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-3-5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-3-5.svg</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Hiérarchie workforce Labor / Craft / Crew</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Isometric organizational diagram showing the IBM Maximo Manage workforce hierarchy: at the top, a Person silhouette icon (identity), connecting down to a Labor record icon (timesheet), branching out to a Craft icon (toolbox + qualification stamp). On the right side, a Crew Type template (blueprint icon with empty slots labeled Craft/Tool/Labor) connected to a Crew instance (3-figure team grouping with crane icon for Tool and small Premium Pay badges). At the bottom right, a larger Crew Work Group container holding 3 mini-crews. Subtle visual separation between template (left/center) and instance (right) sides.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching the C1000-183 series visual language. Vector flat with soft depth shading. Stripe Press / Linear marketing infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Left column: Person → Labor → Craft vertical flow (identity to qualification). Right column: Crew Type (blueprint) → Crew (instance team) → Crew Work Group (regional grouping) vertical flow. Connecting arrow horizontal mid-canvas labeled 'fill' between Craft and Crew Type. Premium Pay badge floats near Craft. Subtle topographic background.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Person blue #3B82F6, Labor slate gray #475569, Craft amber #F59E0B (qualification), Premium Pay red #EF4444 (subtle accent), Crew Type amber #F59E0B (template), Crew teal #1D9E75 (instance), Crew Work Group bold teal #1D9E75 (grouping), white background, topographic pattern at 5% alpha.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion under each entity</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1-3.4 hero (same color system, same isometric perspective).</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks, no 3D render look, no skeuomorphism</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Crews https://www.ibm.com/docs/en/maximo-manage/9.0.0?topic=crews-creating ; lessons 3.1-3.4 hero (visual coherence) ; Stripe Press infographics</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Hero image for lesson 3.5. The hierarchy must clearly separate the template side (Person → Labor → Craft + Premium Pay + Crew Type) from the instance side (Crew → Crew Work Group). Connection arrow 'fill' shows that templates are instantiated. Color amber for templates, teal for instances, blue for identity (Person), gray for capacity (Labor).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/c1000-183-image-prompts.xlsx
+++ b/c1000-183-image-prompts.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -912,6 +912,545 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="220" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-3-6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-3-6.svg</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Les 6 types de Domains Maximo</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Isometric grid layout showing the 6 IBM Maximo Manage domain types as 6 distinct icon boxes arranged in a 3x2 grid: ALN (alphabet letters icon), Numeric (digits 0-9 icon), Numeric Range (slider with min/max bounds), Table (database table with WHERE clause highlighted), Crossover (two records with copy arrows between them), Synonym (two languages speech bubbles). Each box has a distinct color theme but consistent visual language. Bottom of canvas shows a small 'Database Configuration' anchor showing where domains are bound to attributes.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching the C1000-183 series visual language. Vector flat with soft depth shading. Stripe Press / Linear marketing infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3x2 grid of domain type boxes, equal spacing, labeled below. Top row: ALN, Numeric, Numeric Range. Bottom row: Table, Crossover, Synonym. Below grid: small Database Configuration anchor with arrow showing 'binding' connection. Subtle topographic background pattern at 5% opacity.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>ALN slate gray #475569 (static text), Numeric blue #3B82F6 (static numeric), Numeric Range amber #F59E0B (interval), Table teal #1D9E75 (dynamic SQL), Crossover orange #F97316 (propagation), Synonym purple #8B5CF6 (i18n translation), white background, brand topographic pattern at 5% alpha.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion under each box</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1-3.5 hero (same color system, same isometric perspective).</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks, no 3D render look, no skeuomorphism</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Domains https://www.ibm.com/docs/en/maximo-manage/9.0.0?topic=domains-overview ; lessons 3.1-3.5 hero (visual coherence) ; Stripe Press infographics</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Hero image for lesson 3.6. The 6 types must each be visually distinct via icons and color, but the grid layout must communicate they are siblings (alternative choices). Database Configuration anchor reinforces the binding step often forgotten by candidates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="220" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-3-7.svg</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Database Configuration</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>DB Config app showing object/attribute editor + Admin Mode toggle + 4 Object Levels (System/Org/Site/SysOrgSite) + Configure Database action</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading. Stripe Press / Linear infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75 (operational), accent amber #F59E0B (structural), neutral slate #475569, white background, brand topographic teal at 5% alpha</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1-3.6 hero.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-3.6 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Match visual language of previous lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="220" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-3-8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-3-8.svg</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Automation Scripts</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Scripting Engine showing 8 launch points (Object/Attribute/Action/Integration/Publish Channel/Custom Condition/App Bean/Data Bean) with code editor and variables IN/OUT/INOUT/RETURN</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading. Stripe Press / Linear infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75 (operational), accent amber #F59E0B (structural), neutral slate #475569, white background, brand topographic teal at 5% alpha</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1-3.6 hero.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-3.6 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Match visual language of previous lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="220" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-3-9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-3-9.svg</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Workflow Designer</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Workflow Designer canvas with 8 node types (Start/Stop/Condition/Task/Manual Input/Subprocess/Wait/Interaction) connected by transition arrows</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading. Stripe Press / Linear infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75 (operational), accent amber #F59E0B (structural), neutral slate #475569, white background, brand topographic teal at 5% alpha</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1-3.6 hero.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-3.6 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Match visual language of previous lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="220" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-3-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-3-10.svg</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Integration Framework MIF</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>MIF showing Object Structures + JMS/Kafka queues + Publish Channels (outbound) + Enterprise Services (inbound) + Invocation Channels (sync calls) + API Keys</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading. Stripe Press / Linear infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75 (operational), accent amber #F59E0B (structural), neutral slate #475569, white background, brand topographic teal at 5% alpha</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1-3.6 hero.</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-3.6 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Match visual language of previous lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="220" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-3-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-3-11.svg</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Role-Based Apps</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Role-Based Security app with 3 access areas (Application Access + Object Security + Application Options) + Security Templates reusable across groups</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading. Stripe Press / Linear infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75 (operational), accent amber #F59E0B (structural), neutral slate #475569, white background, brand topographic teal at 5% alpha</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1-3.6 hero.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-3.6 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Match visual language of previous lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="220" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-3-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-3-12.svg</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Operational Dashboards</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard layout with 8 card types (Quick Actions, Favorites, KPI value, Table, External content, KPI Chart, KPI Comparison, Work Queues highlighted)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading. Stripe Press / Linear infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75 (operational), accent amber #F59E0B (structural), neutral slate #475569, white background, brand topographic teal at 5% alpha</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1-3.6 hero.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-3.6 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Match visual language of previous lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/c1000-183-image-prompts.xlsx
+++ b/c1000-183-image-prompts.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1451,6 +1451,545 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="220" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-6-1</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-6-1.svg</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Job Plans et Routes</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Job Plan editor with tasks list (Tasks tab), Resources (Labor/Craft/Material/Tool), Flow Control predecessor diagram, Qualifications badges, Nested job plan reference</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading. Stripe Press / Linear infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75 (operational), accent amber #F59E0B (structural), neutral slate #475569, white background, brand topographic teal at 5% alpha</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1-3.12 hero.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-3.12 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Match visual language of S3 lessons hero illustrations. Section 6 Work Management (16% exam weight).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="220" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-6-2</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-6-2.svg</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Condition Monitoring</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Measurement Point on asset showing reading meter + Warning Limits (yellow line) + Upper Limit (red line) crossed → auto-WO generation arrow + MeasurePointWoGenCronTask icon</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading. Stripe Press / Linear infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75 (operational), accent amber #F59E0B (structural), neutral slate #475569, white background, brand topographic teal at 5% alpha</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1-3.12 hero.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-3.12 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Match visual language of S3 lessons hero illustrations. Section 6 Work Management (16% exam weight).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="220" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-6-3</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-6-3.svg</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Preventive Maintenance</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Master PM (template, top) connecting to 4 children PMs (auto-inheriting), each child has Earliest Next Due Date displayed, Job Plan attached, Break from Master flag option</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading. Stripe Press / Linear infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75 (operational), accent amber #F59E0B (structural), neutral slate #475569, white background, brand topographic teal at 5% alpha</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1-3.12 hero.</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-3.12 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Match visual language of S3 lessons hero illustrations. Section 6 Work Management (16% exam weight).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="220" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-6-4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-6-4.svg</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Work Orders</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Work Order with 3 Priority badges (Asset Priority + WO Priority + CALCPRIORITY=calculated), Under Flow Control flag highlighted, 3 source icons (PM, CM, Manual) on left feeding into the WO</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading. Stripe Press / Linear infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75 (operational), accent amber #F59E0B (structural), neutral slate #475569, white background, brand topographic teal at 5% alpha</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1-3.12 hero.</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-3.12 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Match visual language of S3 lessons hero illustrations. Section 6 Work Management (16% exam weight).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="220" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-6-5</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-6-5.svg</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Hero — AI Broker WO Intelligence</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Watson Granite 3.0 8B model icon connected to Maximo via 3 System Properties (mxe.int.aibrokerapikey/url/tenantid), training data flow from WO Description field, recommendations Problem Codes outputted</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading. Stripe Press / Linear infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75 (operational), accent amber #F59E0B (structural), neutral slate #475569, white background, brand topographic teal at 5% alpha</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1-3.12 hero.</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-3.12 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Match visual language of S3 lessons hero illustrations. Section 6 Work Management (16% exam weight).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="220" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-6-6</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-6-6.svg</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Maintenance Cost Rollup</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Asset hierarchy tree (parent + 3 children), each child contributing 4 cost categories (Labor + Material + Tool + Service), arrows aggregating costs upward to parent total</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading. Stripe Press / Linear infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75 (operational), accent amber #F59E0B (structural), neutral slate #475569, white background, brand topographic teal at 5% alpha</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1-3.12 hero.</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-3.12 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Match visual language of S3 lessons hero illustrations. Section 6 Work Management (16% exam weight).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="220" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-6-7</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-6-7.svg</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Inspections Forms</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Inspection Form layout with 7 question type icons (Yes/No, Numeric, Text, Choice, Multi-select, Date, Meter), Conditional questions branching, Follow-up Action + Automation Script triggers, MVI image analysis integration</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading. Stripe Press / Linear infographic aesthetic.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75 (operational), accent amber #F59E0B (structural), neutral slate #475569, white background, brand topographic teal at 5% alpha</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured, neutral business</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills. Visual coherence with lessons 3.1-3.12 hero.</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no detailed human features, no realistic photo textures, no shadow gradients, no text labels (added in HTML), no IBM logos, no Maximo logos, no trademarks</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-3.12 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Match visual language of S3 lessons hero illustrations. Section 6 Work Management (16% exam weight).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/c1000-183-image-prompts.xlsx
+++ b/c1000-183-image-prompts.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1990,6 +1990,622 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="220" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-4-1</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-4-1.svg</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Assets Lifecycle</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Asset record card showing 5 status transitions (Receive→NOT READY, Issue→OPERATING, Return→NOT READY, Downtime→DOWN, Decommission→DECOMMISSIONED) connected by arrows. Asset hierarchy parent/child tree on right side. Rotating Item linkage hint.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-6.7 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>S4 Asset &amp; Inventory (15% exam weight). Match visual language of S3+S6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="220" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-4-2</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-4-2.svg</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Meters et Meter Groups</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Meter dashboard showing 3 types (Continuous gauge for hours/km, Gauge with min/max, Characteristic) attached to assets. Meter Groups containing multiple meters. MeasurePointWoGenCronTask icon scheduling reads.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-6.7 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>S4 Asset &amp; Inventory (15% exam weight). Match visual language of S3+S6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="220" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-4-3</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-4-3.svg</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Failure Codes Hierarchy</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Failure Codes hierarchy diagram (Problem → Cause → Remedy 3-level tree) attached to assets. Reliability Strategies icon (RCM/FMECA framework) on right. ISO 14224 reference badge.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-6.7 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>S4 Asset &amp; Inventory (15% exam weight). Match visual language of S3+S6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="220" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-4-4</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-4-4.svg</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Item Master records</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Item Master record types (Item / Tool / Service) + flags (Rotating? / Lotted? / Capitalized? / Inspect on Receipt?). Item Set partage entre Orgs visualized.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-6.7 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>S4 Asset &amp; Inventory (15% exam weight). Match visual language of S3+S6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="220" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-4-5</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-4-5.svg</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Inventory Settings</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Inventory configuration showing ABC Analysis classes (A/B/C/N), Reorder Points (ROP/EOQ formulas), Cycle Counts frequencies, Inventory Defaults panel.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-6.7 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>S4 Asset &amp; Inventory (15% exam weight). Match visual language of S3+S6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="220" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-4-6</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-4-6.svg</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Inventory Usage app</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Inventory Usage application with 4 Document Types (Issue / Return / Transfer / Receipt) + status workflow (ENTERED → STAGED → SHIPPED → COMPLETE), with Bin/Lot fields highlighted.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-6.7 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>S4 Asset &amp; Inventory (15% exam weight). Match visual language of S3+S6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="220" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-4-7</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-4-7.svg</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Inventory Mobile Apps</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Tablet displaying 3 mobile apps (Issues, Returns, Counts) on warehouse floor with barcode scanner overlay. Storeroom worker silhouette with handheld device.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-6.7 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>S4 Asset &amp; Inventory (15% exam weight). Match visual language of S3+S6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="220" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-4-8</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-4-8.svg</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Count Books</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Count Book showing 7 Sample Types (ALL/BIN/CNTFREQ/ICG/ITEM/ROTATING/TOOLS) + Reconciliation Mismatched tab + Counter Variance Threshold + workflow Generate→Count→Reconcile.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-6.7 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>S4 Asset &amp; Inventory (15% exam weight). Match visual language of S3+S6.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/c1000-183-image-prompts.xlsx
+++ b/c1000-183-image-prompts.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2606,6 +2606,314 @@
         </is>
       </c>
     </row>
+    <row r="29" ht="220" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-7-1</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-7-1.svg</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Planning &amp; Scheduling Apps</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance Scheduler app showing Gantt chart timeline with assignments, Graphical Scheduling app with drag-drop tasks, Resource list on left side</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-6.7 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>S7 Scheduler (11% exam weight). Match visual language of S3+S6+S4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="220" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-7-2</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-7-2.svg</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Scheduler Data Manager</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Scheduler Data Manager interface preparing project records, populating WO/PM data into project, calendar resources sync</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-6.7 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>S7 Scheduler (11% exam weight). Match visual language of S3+S6+S4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="220" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-7-3</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-7-3.svg</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Maximo Optimizer (CPLEX)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Optimization engine icon (IBM ILOG CPLEX) automatically scheduling work, constraints panel (skills + availability + priority), optimized Gantt output</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-6.7 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>S7 Scheduler (11% exam weight). Match visual language of S3+S6+S4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="220" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-7-4</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-7-4.svg</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Scheduling Dashboards</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard with Gantt + resource leveling chart + dispatch board (real-time WO assignment status), KPI tiles for utilization rate</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons 3.1-6.7 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>S7 Scheduler (11% exam weight). Match visual language of S3+S6+S4.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/c1000-183-image-prompts.xlsx
+++ b/c1000-183-image-prompts.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2914,6 +2914,1007 @@
         </is>
       </c>
     </row>
+    <row r="33" ht="220" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-1-1</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-1-1.svg</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Maximo Application Suite</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>MAS architecture diagram showing 5 products on OpenShift platform: Manage (CMMS core), Health (asset health), MVI (visual inspection), Predict (predictive maintenance), Visual Inspection mobile. Cluster icons + container layer.</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons P1 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>P2 lesson — match visual language of P1 lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="220" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-1-2</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-1-2.svg</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Hero — MAS User Administration</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>MAS Admin Center hierarchy: MAS-level user (provisioning across products) → Manage-level user (permissions per app). Entitlements badges + license types (Premium, Base, Limited).</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons P1 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>P2 lesson — match visual language of P1 lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="220" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-1-3</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-1-3.svg</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Add-ons et Industry Solutions</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Industry Solutions catalog visualisé : Oil &amp; Gas, Utilities, Transportation, Aviation, Nuclear, Spatial Asset Management. Each as a colored module connecting to base Manage core.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons P1 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>P2 lesson — match visual language of P1 lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="220" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-2-1</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-2-1.svg</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Chart of Accounts</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>GL Account string composition diagram: 4-segment example (e.g., 6000-200-300-400) with delimiters. GL Account Configuration in Organizations app + segment definitions.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons P1 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>P2 lesson — match visual language of P1 lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="220" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-2-2</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-2-2.svg</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Budget Monitoring</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Budget tracking dashboard: budget allocation per GL account (cards), actuals vs planned (bars), variance alerts (yellow/red), cost rollup arrows from WO to GL.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons P1 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>P2 lesson — match visual language of P1 lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="220" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-2-3</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-2-3.svg</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Asset Depreciation</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>3 depreciation methods comparison: Straight-Line (linear graph), Declining Balance (curved decay), Units-of-Production (variable based usage). Asset value over time.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons P1 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>P2 lesson — match visual language of P1 lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="220" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-5-1</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-5-1.svg</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Contracts</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>4 contract types: Purchase, Lease, Warranty, Service. Each as a folder icon with lifecycle (Draft → Approved → Active → Expired). Master/Revision relationship visualized.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons P1 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>P2 lesson — match visual language of P1 lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="220" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-5-2</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-5-2.svg</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Procurement Flow</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Linear flow MR → PR → PO → Receipt → Invoice with status icons. RFQ branch off PR for vendor bidding. 5 stages clearly labeled.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons P1 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>P2 lesson — match visual language of P1 lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="220" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-5-3</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-5-3.svg</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Receiving et Invoicing</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Receiving workflow: PO arrival → MATRECTRANS row + Inspection (optional WINSP) → Invoice 3-way match (PO + Receipt + Invoice prices reconciled).</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons P1 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>P2 lesson — match visual language of P1 lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="220" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-8-1</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-8-1.svg</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Service Requests</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Service Request lifecycle: ticket creation by customer → classification → triage → escalation to WO. SR icon transitioning to WO icon with arrow.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons P1 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>P2 lesson — match visual language of P1 lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="220" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-8-2</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-8-2.svg</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Service Level Agreements</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>SLA commitment matrix table: Priority levels × Response/Resolution time. Calendar-aware countdown timers with Escalation triggers.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons P1 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>P2 lesson — match visual language of P1 lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="220" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-9-1</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-9-1.svg</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Safety Plans</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Safety Plan record showing 4 categories: Hazards (warning icons), Tag Outs (tags), Lock Outs (LOTO padlock), Precautions (PPE icons). Risk assessment matrix.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons P1 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>P2 lesson — match visual language of P1 lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="220" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>c1000-183-9-2</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>assets/illustrations/lesson-c1000-183-9-2.svg</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Hero — Apply Safety Plans</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Safety Plan application workflow on WO: assignment of LOTO procedure, technician sign-off checklist, completion verification. Prerequisite enforcement before WO start.</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Clean technical isometric illustration matching C1000-183 series visual language. Vector flat with soft depth shading.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Centered isometric composition, 80px padding, subtle topographic background pattern at 5% opacity</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Primary teal #1D9E75, accent amber #F59E0B, neutral slate #475569, white background</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Soft directional from top-left, gentle ambient occlusion</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Professional, didactic, structured</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>1280x480px aspect (cinematic banner). SVG-friendly clean lines and flat fills.</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>no realistic faces, no realistic photo textures, no shadow gradients, no text labels, no IBM/Maximo logos</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>IBM Docs Maximo Manage 9 ; lessons P1 hero (visual coherence)</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>P2 lesson — match visual language of P1 lessons hero illustrations.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
